--- a/data.mn/public/datasets/doctors-national.xlsx
+++ b/data.mn/public/datasets/doctors-national.xlsx
@@ -1,13 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Doctors National" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="English" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Монгол" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -415,6 +416,10 @@
   </sheetPr>
   <dimension ref="A1:B43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="6" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -767,4 +772,370 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B43"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="6" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>он</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>эмч_тоо_нийт</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1925</v>
+      </c>
+      <c r="B2" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>1930</v>
+      </c>
+      <c r="B3" t="n">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>1940</v>
+      </c>
+      <c r="B4" t="n">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>1947</v>
+      </c>
+      <c r="B5" t="n">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>1950</v>
+      </c>
+      <c r="B6" t="n">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>1952</v>
+      </c>
+      <c r="B7" t="n">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>1955</v>
+      </c>
+      <c r="B8" t="n">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>1957</v>
+      </c>
+      <c r="B9" t="n">
+        <v>547</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>1958</v>
+      </c>
+      <c r="B10" t="n">
+        <v>607</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>1960</v>
+      </c>
+      <c r="B11" t="n">
+        <v>873</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>1961</v>
+      </c>
+      <c r="B12" t="n">
+        <v>1022</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>1962</v>
+      </c>
+      <c r="B13" t="n">
+        <v>1093</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>1963</v>
+      </c>
+      <c r="B14" t="n">
+        <v>1216</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>1964</v>
+      </c>
+      <c r="B15" t="n">
+        <v>1373</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>1965</v>
+      </c>
+      <c r="B16" t="n">
+        <v>1511</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>1966</v>
+      </c>
+      <c r="B17" t="n">
+        <v>1671</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>1967</v>
+      </c>
+      <c r="B18" t="n">
+        <v>1820</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>1968</v>
+      </c>
+      <c r="B19" t="n">
+        <v>1983</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>1969</v>
+      </c>
+      <c r="B20" t="n">
+        <v>2106</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>1970</v>
+      </c>
+      <c r="B21" t="n">
+        <v>2259</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>1971</v>
+      </c>
+      <c r="B22" t="n">
+        <v>2415</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>1972</v>
+      </c>
+      <c r="B23" t="n">
+        <v>2578</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>1973</v>
+      </c>
+      <c r="B24" t="n">
+        <v>2738</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>1974</v>
+      </c>
+      <c r="B25" t="n">
+        <v>2720</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>1975</v>
+      </c>
+      <c r="B26" t="n">
+        <v>2920</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>1976</v>
+      </c>
+      <c r="B27" t="n">
+        <v>3056</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>1977</v>
+      </c>
+      <c r="B28" t="n">
+        <v>3184</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>1978</v>
+      </c>
+      <c r="B29" t="n">
+        <v>3334</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>1979</v>
+      </c>
+      <c r="B30" t="n">
+        <v>3547</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>1980</v>
+      </c>
+      <c r="B31" t="n">
+        <v>3686</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>1981</v>
+      </c>
+      <c r="B32" t="n">
+        <v>3881</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>1982</v>
+      </c>
+      <c r="B33" t="n">
+        <v>4070</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>1983</v>
+      </c>
+      <c r="B34" t="n">
+        <v>4234</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>1984</v>
+      </c>
+      <c r="B35" t="n">
+        <v>4371</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>1985</v>
+      </c>
+      <c r="B36" t="n">
+        <v>4595</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>1986</v>
+      </c>
+      <c r="B37" t="n">
+        <v>4870</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>1987</v>
+      </c>
+      <c r="B38" t="n">
+        <v>5192</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>1988</v>
+      </c>
+      <c r="B39" t="n">
+        <v>5485</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>1989</v>
+      </c>
+      <c r="B40" t="n">
+        <v>5715</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>1990</v>
+      </c>
+      <c r="B41" t="n">
+        <v>6180</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>1991</v>
+      </c>
+      <c r="B42" t="n">
+        <v>6132</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>1992</v>
+      </c>
+      <c r="B43" t="n">
+        <v>6053</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>